--- a/data/import/WPimpnotebooks.xlsx
+++ b/data/import/WPimpnotebooks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="87">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -262,7 +262,13 @@
     <t xml:space="preserve">DELL Latitude E5470 i5-6440HQ 8GB RAM, 250 GB SSD, 14” FHD Graphics Radeon 7 M360 + Intel HD Graphics 530, Windows 10, puhastatud kiire, lisatud kontori tarkvara</t>
   </si>
   <si>
-    <t xml:space="preserve">ASUS-X553M_ N3540.jpg</t>
+    <t xml:space="preserve">=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laptops used &gt;used, 2-gen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASUS-X553M__N3540.webp, ASUS-X553M_ N3540.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">E7440 8 RAM, 256 SSD, 14" Full HD 1920 x 1080 pixels </t>
@@ -487,12 +493,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="39.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="5.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="37.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="7.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="7.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.31"/>
@@ -1061,19 +1067,28 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="N23" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="C24" s="1" t="n">
         <v>340018</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>110</v>
@@ -1091,13 +1106,13 @@
         <v>21</v>
       </c>
       <c r="N24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
